--- a/output/pdf_financials_xlsx/LCX.xlsx
+++ b/output/pdf_financials_xlsx/LCX.xlsx
@@ -9958,7 +9958,11 @@
           <t>Prepaids and deposits (Note 5) 15,492</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -10861,7 +10865,11 @@
           <t>Prepaids and deposits (Note 4)</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -11606,7 +11614,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E79" s="5" t="n">
         <v>0.339788</v>
       </c>

--- a/output/pdf_financials_xlsx/LCX.xlsx
+++ b/output/pdf_financials_xlsx/LCX.xlsx
@@ -840,10 +840,10 @@
         <v>82.29000000000001</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>139.617</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>128.51</v>
       </c>
     </row>
     <row r="11">
@@ -915,22 +915,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000123</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003525</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001591</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>6e-06</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.002914</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.044108</v>
+        <v>0.042517</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.049113</v>
+        <v>0.049107</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.062422</v>
+        <v>0.060831</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.069092</v>
+        <v>0.06908599999999999</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -1956,25 +1956,25 @@
         <v>0.306218</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.083454</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.041953</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.022806</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.243</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>59.628</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>3.822</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
@@ -2036,25 +2036,25 @@
         <v>0.306218</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.083454</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.041953</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.022806</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.243</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>59.628</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>3.822</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0</v>
@@ -2516,25 +2516,25 @@
         <v>0.405682</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.665892</v>
+        <v>0.582438</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.6802510000000001</v>
+        <v>0.638298</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.674365</v>
+        <v>0.651559</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.666754</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.636</v>
+        <v>1.393</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>61.022</v>
+        <v>1.394</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>8.93</v>
+        <v>5.108</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>2.989</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -24083,7 +24083,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -27092,7 +27092,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -29094,7 +29094,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -30232,7 +30232,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -31131,7 +31131,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E356" s="5" t="n">
@@ -31849,7 +31849,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">

--- a/output/pdf_financials_xlsx/LCX.xlsx
+++ b/output/pdf_financials_xlsx/LCX.xlsx
@@ -3442,19 +3442,19 @@
         <v>0</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.149</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -3482,19 +3482,19 @@
         <v>0</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.149</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -3642,19 +3642,19 @@
         <v>0.378884</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.146</v>
+        <v>0.11</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>1.044</v>
+        <v>1</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>1.781</v>
+        <v>1.632</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>16.729</v>
+        <v>16.644</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>3.591</v>
+        <v>2.657</v>
       </c>
     </row>
     <row r="76">
@@ -3853,30 +3853,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H80" s="3" t="n">
+        <v>0.0008774067755300999</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0.0004059003145727438</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>0.0008090219521862597</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>0.0004536163899606688</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0.01024156496375977</v>
       </c>
     </row>
     <row r="81">
@@ -4903,19 +4893,19 @@
         <v>0.089142</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>1.348</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>-0.132</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>-2.039</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>-6.68</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>3.349</v>
       </c>
     </row>
     <row r="107">
@@ -5094,13 +5084,13 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.39958</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.4072</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -6050,13 +6040,13 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.39958</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.4072</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -6092,7 +6082,7 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.051821</v>
+        <v>-0.451401</v>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
@@ -6870,7 +6860,11 @@
           <t>Current portion of lease obligations 8</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -7144,7 +7138,11 @@
           <t>Lease obligations 8</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -8047,7 +8045,11 @@
           <t>Current portion of lease obligations</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -8250,7 +8252,11 @@
           <t>Lease obligations</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -9098,7 +9104,11 @@
           <t>Current portion of lease obligations 10 &amp; 19</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -12673,7 +12683,11 @@
           <t>Deferred income tax recovery 14</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -12951,7 +12965,11 @@
           <t>Change in non-cash operating working capital 15</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -14205,7 +14223,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -14696,7 +14718,11 @@
           <t>Deferred income tax recovery 15</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -14832,7 +14858,11 @@
           <t>Change in non-cash operating working capital 16</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -16530,7 +16560,11 @@
           <t>Deferred income tax recovery 16</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -16601,7 +16635,11 @@
           <t>Change in non-cash operating working capital 17</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -16883,7 +16921,11 @@
           <t>Proceeds on private placement 4</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -18157,7 +18199,11 @@
           <t>Change in non-cash operating working capital 16</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -19445,7 +19491,11 @@
           <t>Purchase of equipment (Note 6) -</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -20374,7 +20424,11 @@
           <t>Purchase equipment</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -22358,7 +22412,11 @@
           <t>Cash proceeds from private placement</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E231" s="5" t="n">
         <v>0.5</v>
       </c>
@@ -22429,7 +22487,11 @@
           <t>Share issue costs related to private placement (Note 8)</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E232" s="5" t="n">
         <v>-0.006411</v>
       </c>
@@ -24225,7 +24287,11 @@
           <t>Deferred income tax recovery 14</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -25203,7 +25269,11 @@
           <t>Deferred income tax recovery 15</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -26739,7 +26809,11 @@
           <t>Deferred income tax recovery 16</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
